--- a/data/trans_dic/IMC_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IMC_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad</t>
+          <t>Población con sobrepeso u obesidad (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,74; 71,8</t>
+          <t>65,67; 71,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,88; 76,07</t>
+          <t>70,21; 75,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,5; 76,96</t>
+          <t>70,39; 76,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71,77; 78,92</t>
+          <t>72,14; 79,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,19; 71,33</t>
+          <t>66,27; 71,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,49; 77,5</t>
+          <t>72,62; 77,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,54; 76,37</t>
+          <t>70,01; 76,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>71,71; 76,92</t>
+          <t>71,63; 76,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,92; 70,85</t>
+          <t>66,97; 70,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72,33; 75,88</t>
+          <t>72,29; 76,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71,01; 75,85</t>
+          <t>71,14; 75,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,68; 77,0</t>
+          <t>72,65; 76,99</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,88; 57,74</t>
+          <t>52,94; 57,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,19; 65,69</t>
+          <t>61,1; 65,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,16; 60,53</t>
+          <t>56,16; 60,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,85; 76,71</t>
+          <t>59,9; 75,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,17; 37,84</t>
+          <t>33,01; 37,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,49; 48,53</t>
+          <t>43,68; 48,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,85; 49,63</t>
+          <t>44,96; 49,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,1; 68,05</t>
+          <t>48,51; 68,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,88; 47,32</t>
+          <t>44,0; 47,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,37; 56,85</t>
+          <t>53,29; 56,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,18; 54,27</t>
+          <t>51,29; 54,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55,6; 68,71</t>
+          <t>55,63; 68,87</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,52; 58,51</t>
+          <t>49,51; 58,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,74; 63,19</t>
+          <t>53,61; 63,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,15; 56,91</t>
+          <t>47,75; 57,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,88; 61,36</t>
+          <t>52,01; 60,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,42; 31,92</t>
+          <t>23,73; 31,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,84; 33,75</t>
+          <t>25,02; 34,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,24; 39,85</t>
+          <t>31,58; 39,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,79; 39,73</t>
+          <t>33,0; 39,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,68; 45,19</t>
+          <t>38,79; 45,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,62; 47,87</t>
+          <t>40,79; 47,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,01; 47,36</t>
+          <t>41,26; 47,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,72; 49,27</t>
+          <t>43,64; 49,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,66; 61,05</t>
+          <t>57,54; 61,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,77; 67,39</t>
+          <t>63,71; 67,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,27; 62,57</t>
+          <t>59,15; 62,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,48; 73,01</t>
+          <t>61,62; 72,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,43; 49,1</t>
+          <t>45,47; 48,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,42; 56,0</t>
+          <t>52,62; 56,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,5; 53,91</t>
+          <t>50,56; 54,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,55; 64,93</t>
+          <t>51,47; 65,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,82; 54,35</t>
+          <t>51,98; 54,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,6; 61,01</t>
+          <t>58,61; 61,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55,28; 57,77</t>
+          <t>55,29; 57,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56,95; 65,47</t>
+          <t>56,88; 65,11</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad</t>
+          <t>Población con sobrepeso u obesidad (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>665681; 727018</t>
+          <t>664917; 724264</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>657956; 716247</t>
+          <t>661056; 713759</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>501429; 547357</t>
+          <t>500651; 546022</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>352144; 387215</t>
+          <t>353949; 388886</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>850636; 916657</t>
+          <t>851614; 923307</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>896507; 958399</t>
+          <t>898036; 962151</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>623288; 674853</t>
+          <t>618608; 674020</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>494054; 529962</t>
+          <t>493559; 530343</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1537561; 1627937</t>
+          <t>1538760; 1628758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1575521; 1652799</t>
+          <t>1574531; 1661690</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1132497; 1209706</t>
+          <t>1134595; 1205826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>857395; 908364</t>
+          <t>857005; 908258</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>890735; 972717</t>
+          <t>891754; 971133</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1187707; 1274904</t>
+          <t>1185860; 1270907</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1130541; 1218421</t>
+          <t>1130609; 1219984</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1355307; 1737017</t>
+          <t>1356291; 1705936</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>522516; 596050</t>
+          <t>520007; 596867</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>744711; 830876</t>
+          <t>747848; 826887</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>862235; 954152</t>
+          <t>864312; 952006</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1040622; 1472262</t>
+          <t>1049457; 1490056</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1430571; 1542433</t>
+          <t>1434436; 1546130</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1949857; 2076959</t>
+          <t>1946650; 2070816</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2014416; 2136034</t>
+          <t>2018722; 2148843</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2462071; 3042506</t>
+          <t>2463291; 3049410</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>270845; 320055</t>
+          <t>270787; 321273</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>253601; 298215</t>
+          <t>253025; 299877</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>256590; 303265</t>
+          <t>254463; 305078</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>329904; 390149</t>
+          <t>330698; 387535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>110675; 150870</t>
+          <t>112163; 150351</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>112902; 153430</t>
+          <t>113743; 154815</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>163603; 208713</t>
+          <t>165378; 208256</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>210141; 254639</t>
+          <t>211535; 254921</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>394339; 460743</t>
+          <t>395504; 459264</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>376350; 443495</t>
+          <t>377935; 443127</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>433289; 500399</t>
+          <t>435961; 501006</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>558252; 629139</t>
+          <t>557173; 627989</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1870667; 1980387</t>
+          <t>1866586; 1979827</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2139221; 2260635</t>
+          <t>2137161; 2248259</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1930427; 2038171</t>
+          <t>1926659; 2035985</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2084696; 2475608</t>
+          <t>2089524; 2461197</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1514167; 1636648</t>
+          <t>1515368; 1632779</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1784164; 1905933</t>
+          <t>1790931; 1909836</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1681559; 1795222</t>
+          <t>1683467; 1800318</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1800798; 2268136</t>
+          <t>1798180; 2277050</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3408281; 3574539</t>
+          <t>3418548; 3579984</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3960159; 4123043</t>
+          <t>3961076; 4128824</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3641511; 3805657</t>
+          <t>3642191; 3802574</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3920623; 4507354</t>
+          <t>3915601; 4482208</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IMC_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,67; 71,53</t>
+          <t>65,73; 71,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,21; 75,81</t>
+          <t>70,03; 76,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,39; 76,77</t>
+          <t>70,25; 76,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72,14; 79,26</t>
+          <t>71,0; 77,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,27; 71,85</t>
+          <t>66,28; 71,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,62; 77,8</t>
+          <t>72,65; 77,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,01; 76,28</t>
+          <t>70,23; 76,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>71,63; 76,97</t>
+          <t>71,97; 77,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,97; 70,89</t>
+          <t>66,94; 70,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72,29; 76,29</t>
+          <t>72,4; 76,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71,14; 75,61</t>
+          <t>71,25; 75,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,65; 76,99</t>
+          <t>72,34; 76,62</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,94; 57,65</t>
+          <t>52,91; 57,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,1; 65,48</t>
+          <t>60,93; 65,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,16; 60,6</t>
+          <t>56,23; 60,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,9; 75,34</t>
+          <t>58,22; 62,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,01; 37,89</t>
+          <t>32,97; 37,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,68; 48,29</t>
+          <t>43,33; 48,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,96; 49,52</t>
+          <t>44,92; 49,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,51; 68,87</t>
+          <t>46,3; 50,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,0; 47,43</t>
+          <t>44,04; 47,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,29; 56,69</t>
+          <t>53,54; 56,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,29; 54,6</t>
+          <t>51,27; 54,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55,63; 68,87</t>
+          <t>52,93; 56,09</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,51; 58,74</t>
+          <t>49,87; 58,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,61; 63,54</t>
+          <t>53,16; 62,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,75; 57,25</t>
+          <t>48,28; 56,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,01; 60,95</t>
+          <t>51,8; 60,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,73; 31,81</t>
+          <t>23,57; 32,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,02; 34,06</t>
+          <t>24,52; 33,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,58; 39,76</t>
+          <t>31,29; 40,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,0; 39,77</t>
+          <t>34,28; 40,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,79; 45,05</t>
+          <t>38,61; 44,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,79; 47,83</t>
+          <t>40,79; 47,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,26; 47,42</t>
+          <t>41,08; 47,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,64; 49,18</t>
+          <t>44,08; 49,39</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,54; 61,03</t>
+          <t>57,64; 61,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,71; 67,02</t>
+          <t>63,47; 67,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,15; 62,51</t>
+          <t>59,17; 62,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,62; 72,58</t>
+          <t>59,91; 63,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,47; 48,99</t>
+          <t>45,59; 48,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,62; 56,11</t>
+          <t>52,5; 56,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,56; 54,07</t>
+          <t>50,57; 54,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,47; 65,18</t>
+          <t>50,16; 53,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,98; 54,43</t>
+          <t>52,04; 54,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,61; 61,1</t>
+          <t>58,55; 61,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55,29; 57,73</t>
+          <t>55,08; 57,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56,88; 65,11</t>
+          <t>55,43; 57,83</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>371315</t>
+          <t>405441</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>512297</t>
+          <t>561082</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>883613</t>
+          <t>966523</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>664917; 724264</t>
+          <t>665514; 724771</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>661056; 713759</t>
+          <t>659369; 717436</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>500651; 546022</t>
+          <t>499626; 546581</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>353949; 388886</t>
+          <t>386596; 424150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>851614; 923307</t>
+          <t>851802; 920039</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>898036; 962151</t>
+          <t>898413; 960275</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>618608; 674020</t>
+          <t>620598; 675560</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>493559; 530343</t>
+          <t>540639; 579229</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1538760; 1628758</t>
+          <t>1538033; 1626805</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1574531; 1661690</t>
+          <t>1576952; 1660907</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1134595; 1205826</t>
+          <t>1136411; 1207477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>857005; 908258</t>
+          <t>937211; 992725</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1471279</t>
+          <t>1332835</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1181659</t>
+          <t>1024780</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2652939</t>
+          <t>2357615</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>891754; 971133</t>
+          <t>891323; 973173</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1185860; 1270907</t>
+          <t>1182646; 1269713</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1130609; 1219984</t>
+          <t>1131922; 1219687</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1356291; 1705936</t>
+          <t>1279283; 1383510</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>520007; 596867</t>
+          <t>519437; 593562</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>747848; 826887</t>
+          <t>741914; 826591</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>864312; 952006</t>
+          <t>863532; 949110</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1049457; 1490056</t>
+          <t>982320; 1070195</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1434436; 1546130</t>
+          <t>1435811; 1543884</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1946650; 2070816</t>
+          <t>1955935; 2076896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2018722; 2148843</t>
+          <t>2017754; 2143948</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2463291; 3049410</t>
+          <t>2286084; 2422713</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>360475</t>
+          <t>392190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>232958</t>
+          <t>265813</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>593433</t>
+          <t>658002</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>270787; 321273</t>
+          <t>272749; 320580</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>253025; 299877</t>
+          <t>250889; 296846</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>254463; 305078</t>
+          <t>257275; 301508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>330698; 387535</t>
+          <t>362002; 421654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>112163; 150351</t>
+          <t>111387; 151848</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>113743; 154815</t>
+          <t>111440; 153866</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>165378; 208256</t>
+          <t>163853; 211131</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>211535; 254921</t>
+          <t>244768; 291299</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>395504; 459264</t>
+          <t>393636; 457692</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>377935; 443127</t>
+          <t>377874; 442158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>435961; 501006</t>
+          <t>434017; 497720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>557173; 627989</t>
+          <t>622866; 697849</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2203071</t>
+          <t>2130465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1926915</t>
+          <t>1851675</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4129985</t>
+          <t>3982141</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1866586; 1979827</t>
+          <t>1869898; 1981608</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2137161; 2248259</t>
+          <t>2129022; 2249590</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1926659; 2035985</t>
+          <t>1927368; 2035204</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2089524; 2461197</t>
+          <t>2061408; 2194175</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1515368; 1632779</t>
+          <t>1519462; 1631473</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1790931; 1909836</t>
+          <t>1786836; 1909927</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1683467; 1800318</t>
+          <t>1683836; 1800200</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1798180; 2277050</t>
+          <t>1799395; 1904425</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3418548; 3579984</t>
+          <t>3422415; 3589263</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3961076; 4128824</t>
+          <t>3956573; 4124599</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3642191; 3802574</t>
+          <t>3628009; 3792829</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3915601; 4482208</t>
+          <t>3895791; 4064370</t>
         </is>
       </c>
     </row>
